--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,6 +2883,710 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130215137</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>745961</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7467127</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130214981</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>745549</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7467496</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130212929</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80229</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>745524</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7467226</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130214811</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>745311</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7467292</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130215133</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>745406</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7467640</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130213074</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97710</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>745095</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7467582</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130213144</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>745348</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7467338</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>130212929</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>130214811</v>
       </c>
       <c r="B25" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97710</v>
+        <v>97797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>130213144</v>
       </c>
       <c r="B28" t="n">
-        <v>80228</v>
+        <v>80313</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>130212929</v>
       </c>
       <c r="B24" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>130213144</v>
       </c>
       <c r="B28" t="n">
-        <v>80313</v>
+        <v>80316</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>130212929</v>
       </c>
       <c r="B24" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>130214811</v>
       </c>
       <c r="B25" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>130213144</v>
       </c>
       <c r="B28" t="n">
-        <v>80316</v>
+        <v>80342</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>130214981</v>
       </c>
       <c r="B23" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>130212929</v>
       </c>
       <c r="B24" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>130214811</v>
       </c>
       <c r="B25" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>130213144</v>
       </c>
       <c r="B28" t="n">
-        <v>80342</v>
+        <v>80344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>130215137</v>
       </c>
       <c r="B22" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>130215133</v>
       </c>
       <c r="B26" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>130213074</v>
       </c>
       <c r="B27" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79640938</v>
+        <v>79640923</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745152.8324291313</v>
+        <v>745728</v>
       </c>
       <c r="R2" t="n">
-        <v>7467680.729044255</v>
+        <v>7467361</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79640930</v>
+        <v>79640925</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745418.8500115064</v>
+        <v>745657</v>
       </c>
       <c r="R3" t="n">
-        <v>7467246.946511991</v>
+        <v>7467367</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79640924</v>
+        <v>79640920</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745672.4943882838</v>
+        <v>745827</v>
       </c>
       <c r="R4" t="n">
-        <v>7467368.828593766</v>
+        <v>7467204</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79640709</v>
+        <v>79640922</v>
       </c>
       <c r="B5" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745122.4439089142</v>
+        <v>745739</v>
       </c>
       <c r="R5" t="n">
-        <v>7467497.557149381</v>
+        <v>7467298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2019-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,57 +1056,66 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79640932</v>
+        <v>127385564</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>1365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745254.4875651553</v>
+        <v>745557</v>
       </c>
       <c r="R6" t="n">
-        <v>7467435.642605631</v>
+        <v>7467083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1142,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,65 +1164,75 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79640931</v>
+        <v>127385565</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745305.3471578902</v>
+        <v>745557</v>
       </c>
       <c r="R7" t="n">
-        <v>7467416.932233633</v>
+        <v>7467088</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1259,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,65 +1281,75 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79640925</v>
+        <v>127385566</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>1365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745657.0234737562</v>
+        <v>745560</v>
       </c>
       <c r="R8" t="n">
-        <v>7467367.406680777</v>
+        <v>7467088</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,22 +1376,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Täckning 10 - 25%</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1444,30 +1398,26 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79640928</v>
+        <v>127385567</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,34 +1425,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>1365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745493.9512595645</v>
+        <v>745562</v>
       </c>
       <c r="R9" t="n">
-        <v>7467176.689443631</v>
+        <v>7467089</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1493,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,30 +1515,26 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79640927</v>
+        <v>127385568</v>
       </c>
       <c r="B10" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,34 +1542,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>1365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745585.4721829097</v>
+        <v>745566</v>
       </c>
       <c r="R10" t="n">
-        <v>7467318.360013066</v>
+        <v>7467090</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1610,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,65 +1632,75 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79640939</v>
+        <v>127385569</v>
       </c>
       <c r="B11" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>1365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745337.1030285552</v>
+        <v>745479</v>
       </c>
       <c r="R11" t="n">
-        <v>7467636.082705835</v>
+        <v>7467164</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1727,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1780,65 +1749,75 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79640923</v>
+        <v>127385571</v>
       </c>
       <c r="B12" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>1365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Malmberget Vitåfors, Lu lm</t>
+          <t>Linaälven, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745728.1659809604</v>
+        <v>745478</v>
       </c>
       <c r="R12" t="n">
-        <v>7467361.477304989</v>
+        <v>7467168</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,22 +1844,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Täckning 0 - 10%</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,68 +1866,68 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tony Svensson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98311724</v>
+        <v>130211810</v>
       </c>
       <c r="B13" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101298</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Linaälven-Koskullskulle, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745609.236594436</v>
+        <v>745754</v>
       </c>
       <c r="R13" t="n">
-        <v>7467446.008450474</v>
+        <v>7467291</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,22 +1951,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,65 +1971,68 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Jennifer Sondell</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98309421</v>
+        <v>130215172</v>
       </c>
       <c r="B14" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101298</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>1365</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Linaälven-Koskullskulle, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745222.9136929773</v>
+        <v>745771</v>
       </c>
       <c r="R14" t="n">
-        <v>7467715.987898734</v>
+        <v>7467284</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,22 +2056,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,65 +2076,68 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>98311731</v>
+        <v>130215176</v>
       </c>
       <c r="B15" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101298</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Linaälven-Koskullskulle, Lu lm</t>
+          <t>Gällivare kommun, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745585.100386649</v>
+        <v>745759</v>
       </c>
       <c r="R15" t="n">
-        <v>7467462.492989719</v>
+        <v>7467290</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,22 +2161,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,66 +2181,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Irma Lindfors</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Robert Flygare</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>114653703</v>
+        <v>98311724</v>
       </c>
       <c r="B16" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>1962</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven-Koskullskulle, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745528</v>
+        <v>745609</v>
       </c>
       <c r="R16" t="n">
-        <v>7467372</v>
+        <v>7467446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2317,12 +2262,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2337,27 +2282,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>114653693</v>
+        <v>96652328</v>
       </c>
       <c r="B17" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2365,41 +2305,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Patjanenvägen-Linaälv, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745558</v>
+        <v>746019</v>
       </c>
       <c r="R17" t="n">
-        <v>7467161</v>
+        <v>7467107</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2423,12 +2362,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,33 +2376,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>114653695</v>
+        <v>79640939</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,38 +2406,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102999</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Malmberget Vitåfors, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745515</v>
+        <v>745337</v>
       </c>
       <c r="R18" t="n">
-        <v>7467212</v>
+        <v>7467636</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2529,12 +2460,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2549,62 +2480,57 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Matilda Andrén</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>114653919</v>
+        <v>98309421</v>
       </c>
       <c r="B19" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103044</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven-Koskullskulle, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>746026</v>
+        <v>745223</v>
       </c>
       <c r="R19" t="n">
-        <v>7467226</v>
+        <v>7467716</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2631,12 +2557,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-29</t>
+          <t>2021-08-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,27 +2577,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emmy Ransgart</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114775918</v>
+        <v>98311731</v>
       </c>
       <c r="B20" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2679,43 +2600,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103001</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>Linaälven-Koskullskulle, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745521</v>
+        <v>745585</v>
       </c>
       <c r="R20" t="n">
-        <v>7467209</v>
+        <v>7467463</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2742,12 +2654,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2762,74 +2674,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Robert Flygare</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114775926</v>
+        <v>102080927</v>
       </c>
       <c r="B21" t="n">
-        <v>57680</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103001</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Malmberget, Lu lm</t>
+          <t>..., Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745211</v>
+        <v>746031</v>
       </c>
       <c r="R21" t="n">
-        <v>7467383</v>
+        <v>7467081</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,12 +2751,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2873,22 +2771,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Maj Aspebo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mats Williamson</t>
+          <t>Maj Aspebo, Vivi Eriksson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130215137</v>
+        <v>130214981</v>
       </c>
       <c r="B22" t="n">
-        <v>97834</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,21 +2794,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745961</v>
+        <v>745549</v>
       </c>
       <c r="R22" t="n">
-        <v>7467127</v>
+        <v>7467496</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2978,56 +2876,52 @@
           <t>Hanna Vestman</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130214981</v>
+        <v>79640931</v>
       </c>
       <c r="B23" t="n">
-        <v>91725</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Malmberget Vitåfors, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745549</v>
+        <v>745305</v>
       </c>
       <c r="R23" t="n">
-        <v>7467496</v>
+        <v>7467417</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3051,12 +2945,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3071,22 +2965,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Hanna Vestman</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130212929</v>
+        <v>130213144</v>
       </c>
       <c r="B24" t="n">
-        <v>80345</v>
+        <v>80460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3094,21 +2988,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3118,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745524</v>
+        <v>745348</v>
       </c>
       <c r="R24" t="n">
-        <v>7467226</v>
+        <v>7467338</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3184,53 +3078,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130214811</v>
+        <v>79640928</v>
       </c>
       <c r="B25" t="n">
-        <v>57851</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Malmberget Vitåfors, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745311</v>
+        <v>745494</v>
       </c>
       <c r="R25" t="n">
-        <v>7467292</v>
+        <v>7467177</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3254,12 +3143,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,22 +3163,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anton Andersson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130215133</v>
+        <v>79640930</v>
       </c>
       <c r="B26" t="n">
-        <v>97834</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3297,37 +3186,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Malmberget Vitåfors, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745406</v>
+        <v>745419</v>
       </c>
       <c r="R26" t="n">
-        <v>7467640</v>
+        <v>7467247</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3351,12 +3240,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3371,26 +3260,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Irma Lindfors</t>
+          <t>Tony Svensson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hanna Vestman</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
-        </is>
-      </c>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130213074</v>
+        <v>130212929</v>
       </c>
       <c r="B27" t="n">
-        <v>97834</v>
+        <v>80461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,21 +3283,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3422,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745095</v>
+        <v>745524</v>
       </c>
       <c r="R27" t="n">
-        <v>7467582</v>
+        <v>7467226</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3488,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130213144</v>
+        <v>79640936</v>
       </c>
       <c r="B28" t="n">
-        <v>80344</v>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3499,37 +3384,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gällivare kommun, Lu lm</t>
+          <t>Malmberget Vitåfors, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745348</v>
+        <v>745059</v>
       </c>
       <c r="R28" t="n">
-        <v>7467338</v>
+        <v>7467470</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3553,12 +3438,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,19 +3458,2221 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>79640938</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>745153</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7467681</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130214811</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>745311</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7467292</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Irma Lindfors</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130215024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>745428</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7467462</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>114653827</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>745866</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7467077</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-04-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>inge Karlsson Alalahti</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>114653695</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>745515</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7467212</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>114653692</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>745602</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7467097</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>114653693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>745558</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7467161</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>114653707</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>745643</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7467228</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114775918</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>745521</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7467209</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>114775926</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>745211</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7467383</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mats Williamson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>114653703</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>745528</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7467372</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Matilda Andrén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>79640926</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>745476</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7467324</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>114653919</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Malmberget, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>746026</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7467226</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-05-29</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emmy Ransgart</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>79640927</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>745585</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7467318</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>102080930</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>..., Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>745986</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7467065</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-07-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maj Aspebo</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maj Aspebo, Vivi Eriksson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130213074</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>745095</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7467582</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Jennifer Sondell</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
+      <c r="AY44" t="inlineStr">
         <is>
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130215133</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>745406</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7467640</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130215137</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gällivare kommun, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>745961</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7467127</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Irma Lindfors</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Hanna Vestman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>79640919</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>745878</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7467072</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>79640709</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>745122</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7467498</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>79640924</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>745672</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7467369</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>79640932</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Malmberget Vitåfors, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>745254</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7467436</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2019-08-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39720-2025 artfynd.xlsx
+++ b/artfynd/A 39720-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640925</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640922</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385565</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385566</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385567</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385568</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385569</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127385571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130211810</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215172</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2194,6 +2264,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215176</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2291,6 +2366,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98311724</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96652328</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2586,6 +2676,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98309421</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2683,6 +2778,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98311731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2780,6 +2880,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102080927</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2877,6 +2982,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130214981</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2974,6 +3084,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640931</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3075,6 +3190,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213144</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3172,6 +3292,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640928</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3269,6 +3394,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640930</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3370,6 +3500,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130212929</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3467,6 +3602,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640936</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3564,6 +3704,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640938</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3666,6 +3811,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130214811</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3765,6 +3915,11 @@
       <c r="AY31" t="inlineStr">
         <is>
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215024</t>
         </is>
       </c>
     </row>
@@ -3872,6 +4027,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653827</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3973,6 +4133,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653695</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4074,6 +4239,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653692</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4175,6 +4345,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653693</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4276,6 +4451,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653707</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4382,6 +4562,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775918</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4488,6 +4673,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114775926</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4589,6 +4779,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653703</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4691,6 +4886,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640926</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4788,6 +4988,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114653919</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4885,6 +5090,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640927</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4982,6 +5192,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102080930</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5083,6 +5298,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130213074</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5184,6 +5404,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215133</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5285,6 +5510,11 @@
           <t>Tillståndskonsulter Naalojärvi-Messaure</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130215137</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5382,6 +5612,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640919</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5479,6 +5714,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640709</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5576,6 +5816,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640924</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5673,8 +5918,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79640932</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>